--- a/src/tests/loader/jmmi_invalid.xlsx
+++ b/src/tests/loader/jmmi_invalid.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="clean_data" sheetId="1" state="visible" r:id="rId3"/>
@@ -52,7 +52,7 @@
     <t xml:space="preserve">old_value</t>
   </si>
   <si>
-    <t xml:space="preserve">question</t>
+    <t xml:space="preserve">variable</t>
   </si>
   <si>
     <t xml:space="preserve">change_type</t>
@@ -142,16 +142,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -292,15 +288,15 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -333,29 +329,29 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -396,19 +392,19 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -440,18 +436,18 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -486,7 +482,7 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -533,12 +529,12 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>3</v>
       </c>
     </row>
